--- a/notti_NOV.xlsx
+++ b/notti_NOV.xlsx
@@ -1,6 +1,6 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x15 xr xr6 xr10">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20417"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\seria\Desktop\Repositories\shifter\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{71F9E9BE-94B9-47B2-8C5C-47E8B36156B1}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7815E901-4BAB-45D5-AB0E-244B407586B8}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="26835" windowHeight="12060"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="26835" windowHeight="12060" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="notti_NOV" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="18" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -863,7 +863,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:A6"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -873,29 +873,19 @@
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A2" s="1">
-        <v>45966</v>
-      </c>
+      <c r="A2" s="1"/>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A3" s="1">
-        <v>45976</v>
-      </c>
+      <c r="A3" s="1"/>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A4" s="1">
-        <v>45978</v>
-      </c>
+      <c r="A4" s="1"/>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A5" s="1">
-        <v>45980</v>
-      </c>
+      <c r="A5" s="1"/>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A6" s="1">
-        <v>45986</v>
-      </c>
+      <c r="A6" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/notti_NOV.xlsx
+++ b/notti_NOV.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\seria\Desktop\Repositories\shifter\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6EF90BED-A26A-43A8-ACFA-FF08E5EB6F9E}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48E55DB5-D70A-4033-A803-104E1F4791ED}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="26835" windowHeight="12060" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -876,7 +876,9 @@
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A2" s="1"/>
+      <c r="A2" s="1">
+        <v>45967</v>
+      </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" s="1"/>
